--- a/output/2026-09-20_22_Croazia_Istarska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-20_22_Croazia_Istarska_Componentistica_Ventilazione_industriale.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda reale verificata (gruppo con sede legale a Podsused/Šenkovec, filiale a Pula-Galižana, ~226 dipendenti gruppo). Ingrosso di metalli, materie plastiche industriali, cuscinetti, minuteria, materiale elettrico e utensili. Non risultano prodotti specifici di ventilazione industriale nel catalogo pubblico: fit debole/adiacente. Email da riconfermare indipendentemente.</t>
+          <t>Azienda reale verificata (gruppo con sede legale a Podsused/Šenkovec, filiale a Pula-Galižana, ~226 dipendenti gruppo). Ingrosso di metalli, materie plastiche industriali, cuscinetti, minuteria, materiale elettrico e utensili. Non risultano prodotti specifici di ventilazione industriale nel catalogo pubblico: fit debole/adiacente. Email da riconfermare indipendentemente. [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
